--- a/literature-review/phase_7.3/Paper Dictionary.xlsx
+++ b/literature-review/phase_7.3/Paper Dictionary.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1070,228 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>PCFJudge: Permutation-Consensus Listwise Judging for Robust Factuality Evaluation</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.20562v2</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Introduces PCFJudge, an inference-time multi-run consensus method that reruns the same factuality-first listwise prompt over multiple orderings of the same candidate set and aggregates results to cancel out order sensitivity. Directly targets the instability of LLM judges under presentation variations without requiring multiple model families.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Addresses order/position bias with a practical, single-model multi-run approach. 2026 venue. Directly applicable to factuality checking (same task as Phase 7.3 C1). No extra API keys needed — same model, multiple calls.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Focuses on listwise ranking rather than binary PASS/FAIL per criterion. Adds cost proportional to number of orderings tested.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>For LectureBench Phase 7.3, PCFJudge's consensus principle could be applied to C1 (answer correctness) by running the reviewer twice with shuffled claim order and requiring agreement. However, G-Eval structured form-filling already reduces order sensitivity — PCFJudge's main benefit is marginal for binary criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Harnessing Multiple Large Language Models: A Survey on LLM Ensemble</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2502.18036v6</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>First systematic survey of LLM ensemble methods for downstream inference. Categorizes approaches into output aggregation (majority voting, weighted voting), model selection, and mixture-of-experts. Finds that ensemble methods consistently outperform single-model baselines on reasoning and factuality tasks but add latency and cost.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Comprehensive taxonomy of ensemble strategies. Covers cost-benefit tradeoffs. Directly relevant to deciding whether multi-judge adds value over single-judge for structured QA review.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Does not specifically address ensemble for QA benchmark validation (filtering, not generation). Most studies focus on generation tasks, not binary PASS/FAIL criteria checking.</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Confirms majority voting as the simplest and most robust aggregation strategy if multi-judge is adopted. For LectureBench, majority vote across 2 judges (Claude + GPT-4o) on borderline cases is a lightweight option if Phase 7.3 single-judge produces high disagreement rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>PRD: Peer Rank and Discussion Improve Large Language Model based Evaluations</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2307.02762v3</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Proposes Peer Rank and Discussion (PRD), where multiple LLMs independently evaluate answers, then discuss disagreements before producing a final consensus score. Compared to single-LLM evaluation, PRD reduces position bias and self-enhancement bias. Finds that discussion between judges is more effective than simple majority voting.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Shows that multi-judge discussion (not just voting) further reduces bias beyond single-judge structured prompting. Foundational paper for multi-judge methodology.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Focuses on open-ended QA ranking, not binary PASS/FAIL criteria. Discussion protocol is expensive — each disagreement triggers a second round of API calls.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>PRD's discussion mechanism is most valuable for subjective open-ended scoring (Phase 8 LLM-judge 1-5 scale), not for Phase 7.3's binary criteria checks. For binary PASS/FAIL, simple majority vote is sufficient and cheaper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ChatEval: Towards Better LLM-based Evaluators through Multi-Agent Debate</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2309.17012</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Introduces ChatEval, a multi-agent debate framework where multiple LLM evaluators with different personas argue about the quality of a response before reaching a consensus score. Multi-agent debate outperforms single-judge evaluation on MT-Bench and other open-ended benchmarks, especially for nuanced quality dimensions.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Multi-agent debate with diverse personas reduces systematic blind spots. Strong empirical results on open-ended evaluation benchmarks. Introduces persona diversity as a way to simulate inter-annotator variation.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>High complexity and cost — each evaluation requires multiple agents and multiple debate rounds. Designed for open-ended NLG evaluation, not factuality checking against source text.</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>ChatEval's persona diversity principle is most valuable for Phase 8 LLM-judge scoring where answer quality is subjective. For Phase 7.3's factuality checks (C1 claim verification), the task is objective enough that debate adds minimal signal over a structured single-judge prompt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Learning an Efficient Multi-Turn Dialogue Evaluator from Multiple LLM Judges</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2508.00454v4</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Proposes training a lightweight evaluator distilled from multiple LLM judges to produce reliable dialogue quality scores. Shows that aggregating judgments from multiple LLMs before distillation reduces systematic biases present in any single model. Achieves higher inter-rater reliability than any single judge alone.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Demonstrates empirically that multi-judge aggregation reduces systematic bias in automated evaluation. The distillation approach produces a cheaper inference-time evaluator after training.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Requires a training phase to distill the ensemble, which is expensive and not feasible for a one-off benchmark validation task like LectureBench Phase 7.3.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Confirms the principle that multi-judge aggregation reduces bias, but the distillation approach is not practical for LectureBench. The relevant finding is that 2-3 judge majority vote achieves most of the bias reduction benefit without distillation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Systematic Evaluation of LLM-as-a-Judge in LLM Alignment Tasks: Explainable Metrics and Diverse Prompt Templates</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2408.13006v2</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Proposes explainable metrics (Cohen's Kappa, Krippendorff's alpha) to measure LLM judge reliability, and evaluates how prompt template diversity affects consistency. Finds that LLM judges show high internal inconsistency — the same judge with different prompt templates can disagree 15-25% of the time on the same input.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Introduces quantitative reliability metrics (Kappa, Krippendorff's alpha) applicable to any LLM judge setup. The 15-25% inconsistency finding is directly relevant to assessing whether single-judge Phase 7.3 is reliable enough.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Focuses on alignment tasks (RLHF), not structured criteria-grounded QA review. Inconsistency rates may be lower for binary PASS/FAIL criteria than for 1-5 holistic scoring.</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>The 15-25% inconsistency finding argues for reporting judge reliability metrics (Kappa between two runs with different prompt seeds) in the paper's Phase 7.3 methodology section. This strengthens credibility without requiring a full second-model review pass.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>

--- a/literature-review/phase_7.3/Paper Dictionary.xlsx
+++ b/literature-review/phase_7.3/Paper Dictionary.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1292,6 +1292,43 @@
         </is>
       </c>
     </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Judging Against the Reference: Uncovering Knowledge-Driven Failures in LLM-Judges on QA Evaluation</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2601.07506v1</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Identifies a critical failure mode in reference-based LLM QA evaluation: when the provided reference text conflicts with the judge model's parametric (training) knowledge, the judge systematically favors its own prior over the reference, producing unreliable scores. Constructs a benchmark of knowledge-conflicting QA pairs to study this phenomenon and shows it substantially degrades evaluation fidelity across multiple judge models.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Directly relevant to criteria-grounded factual verification against source text (Phase 7.3 Q4). 2026 paper. Identifies a concrete, testable failure mode — not a vague bias concern. Provides a clear mitigation direction: cross-family judges are less likely to share the same parametric knowledge bias.</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Does not specifically test multi-judge setups as the mitigation. Focuses on QA evaluation fidelity rather than benchmark curation (filtering) tasks. Does not study binary PASS/FAIL rubrics — uses continuous scoring.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>For LectureBench Q4: lecture content (especially cutting-edge ML topics from MIT/Stanford/NYU) may conflict with Claude's parametric knowledge. Lee et al. (2026) argues this is a real failure mode for reference-based judging. The cross-family optional reviewer (GPT-4o) in D1 gains additional justification specifically for Q4 in lectures covering recent or specialized content. This strengthens the case for the optional Kappa reliability check (D8b): if Kappa &lt; 0.7, the disagreements are likely driven by knowledge conflicts, not random noise.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>

--- a/literature-review/phase_7.3/Paper Dictionary.xlsx
+++ b/literature-review/phase_7.3/Paper Dictionary.xlsx
@@ -489,11 +489,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -1329,6 +1329,80 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>LLM-as-a-Judge: Automated Evaluation of Search Query Parsing Using Large Language Models</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/journals/big-data/articles/10.3389/fdata.2025.1611389/full</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Proposes an LLM-as-judge framework for structured Pass/Fail evaluation of search query parsing outputs, achieving ~90% agreement with human judgments. Introduces contextual prompt routing to reduce hallucinations. Validated on small- and large-scale datasets in a real-world structured output evaluation setting.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Peer-reviewed, published in Frontiers in Big Data (2025). Directly validates LLM-based structured Pass/Fail evaluation reliability (~90% human agreement), supporting single-judge structured criteria evaluation for Q1. Closest published analogue to Phase 7.3's binary accept/reject rubric.</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Evaluates structured output parsing (JSON), not QA pair correctness. Does not study same-model review or knowledge-conflict failure modes. Domain differs from lecture video QA.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Supports Q1 decision: LLM single-judge is reliable for structured Pass/Fail tasks. Peer-reviewed alternative to the unreviewed Ho et al. (2025) preprint for structured evaluation reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Beyond Pointwise Scores: Decomposed Criteria-Based Evaluation of LLM Responses</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>https://aclanthology.org/2025.emnlp-industry.136/</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Introduces DeCE, a decomposed LLM evaluation framework separating precision and recall via instance-specific criteria automatically extracted from gold answers. Applied to legal QA with multi-jurisdictional reasoning and citation grounding, achieving r=0.78 with expert judgments vs r=0.35 for pointwise LLM scoring and r=0.12 for traditional metrics.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Published at EMNLP 2025 Industry Track (peer-reviewed). Directly validates the G-Eval form-filling / decomposed criteria approach used in Phase 7.3's rubric. Shows decomposed criteria evaluation substantially outperforms pointwise scoring in expert domains (legal QA), which is analogous to structured academic lecture QA.</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Focuses on legal QA, not video lecture QA. Criteria are automatically extracted from gold answers rather than predefined; Phase 7.3 uses fixed predefined criteria. Evaluates answer quality, not benchmark curation filtering.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Supports Q2 decision: decomposed criteria-based evaluation (our G-Eval rubric with Criterion 1/2/3) achieves higher human correlation than holistic pointwise scoring. Peer-reviewed EMNLP 2025 publication strengthens rubric design justification.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>

--- a/literature-review/phase_7.3/Paper Dictionary.xlsx
+++ b/literature-review/phase_7.3/Paper Dictionary.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +63,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -124,6 +138,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -499,6 +522,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -513,6 +537,11 @@
       <c r="E1" s="5" t="n"/>
       <c r="F1" s="5" t="n"/>
       <c r="G1" s="6" t="n"/>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LLM-as-Judge for QA Benchmark Validation (LectureBench Phase 7.3)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="22" customHeight="1">
@@ -551,6 +580,11 @@
           <t>How Current Paper Resolves Gaps</t>
         </is>
       </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Venue / Peer-Reviewed?</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -588,6 +622,11 @@
           <t>LectureBench uses structured checklist prompting (not open-ended) which mitigates self-enhancement bias; same-model review is acceptable per Ho et al. 2025 for structured QA.</t>
         </is>
       </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>✓ NeurIPS 2023</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -625,6 +664,11 @@
           <t>LectureBench adopts G-Eval's form-filling paradigm (structured sub-scores per criterion) but grounds each score in verifiable source chunk text, limiting self-preference drift.</t>
         </is>
       </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>✓ EMNLP 2023</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -662,6 +706,11 @@
           <t>LectureBench adopts the rubric-per-criterion principle but uses Claude Sonnet 4.6 prompted with task-specific criteria rather than a fine-tuned evaluator, keeping the pipeline simple.</t>
         </is>
       </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>✓ ICLR 2024</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -699,6 +748,11 @@
           <t>Key finding directly answers Q1: same-model review is acceptable for structured QA. LectureBench can use Claude Sonnet 4.6 as both generator and reviewer without circularity risk.</t>
         </is>
       </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -736,6 +790,11 @@
           <t>Supports the general validity of LLM judges in structured evaluation pipelines; reinforces using a strong model (Claude Sonnet 4.6 or GPT-4o) as reviewer.</t>
         </is>
       </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -773,6 +832,11 @@
           <t>LectureBench reviewer verifies each answer claim against cited chunk text (analogous to FActScore's atomic verification). Frame captions convert visual content to text, enabling text-only correctness checking.</t>
         </is>
       </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>✓ EMNLP 2023</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -810,6 +874,11 @@
           <t>RAGAS's faithfulness criterion (answer claims supported by retrieved context) directly informs LectureBench's answer correctness check: the reviewer verifies each answer against cited chunk text.</t>
         </is>
       </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>✓ EACL 2024</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -847,6 +916,11 @@
           <t>Directly motivates the -10s span gap rejection criterion in LectureBench: adjacent chunks are single-hop in disguise. Reviewer must reject multi-hop questions where both spans map to the same or adjacent chunks.</t>
         </is>
       </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>✓ ACL 2019</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -884,6 +958,11 @@
           <t>Supports the LectureBench design: multi-hop questions should require separate retrieval steps from non-adjacent lecture segments, validating our adjacency rejection criterion.</t>
         </is>
       </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2024) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -921,6 +1000,11 @@
           <t>Reinforces using structured sub-criterion prompting (our form-filling approach) to mitigate SPB. Combined with Ho et al. 2025 finding of no SPB in structured QA, the LectureBench reviewer design is well-supported.</t>
         </is>
       </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -958,6 +1042,11 @@
           <t>Validates LectureBench's design choice of step-level (span-level) evaluation over answer-only metrics. Supports using span plausibility as a review criterion in Phase 7.3.</t>
         </is>
       </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -995,6 +1084,11 @@
           <t>Explains why SPB is less of a risk in LectureBench: the reviewer is verifying chunk-grounded factual claims (not stylistically similar to its training distribution), so perplexity familiarity does not apply in the same way.</t>
         </is>
       </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>✓ NeurIPS 2024 Workshop (Safe Generative AI)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1032,6 +1126,11 @@
           <t>LectureBench's ±15–30s span precision is actually better than EduVidQA's ±35.4s. If EduVidQA is accepted without tightening, LectureBench can make the same choice and cite this precedent.</t>
         </is>
       </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>✓ EMNLP 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1069,6 +1168,11 @@
           <t>Represents the ideal; LectureBench trades span precision for scale. Justifies using tIoU@0.3 as the primary threshold (more forgiving of ±15–30s error) rather than tIoU@0.5.</t>
         </is>
       </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -1106,6 +1210,11 @@
           <t>For LectureBench Phase 7.3, PCFJudge's consensus principle could be applied to C1 (answer correctness) by running the reviewer twice with shuffled claim order and requiring agreement. However, G-Eval structured form-filling already reduces order sensitivity — PCFJudge's main benefit is marginal for binary criteria.</t>
         </is>
       </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1143,6 +1252,11 @@
           <t>Confirms majority voting as the simplest and most robust aggregation strategy if multi-judge is adopted. For LectureBench, majority vote across 2 judges (Claude + GPT-4o) on borderline cases is a lightweight option if Phase 7.3 single-judge produces high disagreement rates.</t>
         </is>
       </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -1180,6 +1294,11 @@
           <t>PRD's discussion mechanism is most valuable for subjective open-ended scoring (Phase 8 LLM-judge 1-5 scale), not for Phase 7.3's binary criteria checks. For binary PASS/FAIL, simple majority vote is sufficient and cheaper.</t>
         </is>
       </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2023) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1217,6 +1336,11 @@
           <t>ChatEval's persona diversity principle is most valuable for Phase 8 LLM-judge scoring where answer quality is subjective. For Phase 7.3's factuality checks (C1 claim verification), the task is objective enough that debate adds minimal signal over a structured single-judge prompt.</t>
         </is>
       </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>✓ ICLR 2024</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -1254,6 +1378,11 @@
           <t>Confirms the principle that multi-judge aggregation reduces bias, but the distillation approach is not practical for LectureBench. The relevant finding is that 2-3 judge majority vote achieves most of the bias reduction benefit without distillation.</t>
         </is>
       </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2025) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1291,6 +1420,11 @@
           <t>The 15-25% inconsistency finding argues for reporting judge reliability metrics (Kappa between two runs with different prompt seeds) in the paper's Phase 7.3 methodology section. This strengthens credibility without requiring a full second-model review pass.</t>
         </is>
       </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2024) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -1328,6 +1462,11 @@
           <t>For LectureBench Q4: lecture content (especially cutting-edge ML topics from MIT/Stanford/NYU) may conflict with Claude's parametric knowledge. Lee et al. (2026) argues this is a real failure mode for reference-based judging. The cross-family optional reviewer (GPT-4o) in D1 gains additional justification specifically for Q4 in lectures covering recent or specialized content. This strengthens the case for the optional Kappa reliability check (D8b): if Kappa &lt; 0.7, the disagreements are likely driven by knowledge conflicts, not random noise.</t>
         </is>
       </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>✗ arXiv preprint (2026) — not peer-reviewed</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1365,6 +1504,11 @@
           <t>Supports Q1 decision: LLM single-judge is reliable for structured Pass/Fail tasks. Peer-reviewed alternative to the unreviewed Ho et al. (2025) preprint for structured evaluation reliability.</t>
         </is>
       </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>✓ Frontiers in Big Data (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -1400,6 +1544,11 @@
       <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Supports Q2 decision: decomposed criteria-based evaluation (our G-Eval rubric with Criterion 1/2/3) achieves higher human correlation than holistic pointwise scoring. Peer-reviewed EMNLP 2025 publication strengthens rubric design justification.</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>✓ EMNLP 2025 Industry Track</t>
         </is>
       </c>
     </row>

--- a/literature-review/phase_7.3/Paper Dictionary.xlsx
+++ b/literature-review/phase_7.3/Paper Dictionary.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>✓ EACL 2024</t>
+          <t>✓ EACL 2024 (System Demonstrations track)</t>
         </is>
       </c>
     </row>
